--- a/data/00988A/20260427.xlsx
+++ b/data/00988A/20260427.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="218">
-  <si>
-    <t xml:space="preserve">資料日期：115/04/23</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="221">
+  <si>
+    <t xml:space="preserve">資料日期：115/04/24</t>
   </si>
   <si>
     <t xml:space="preserve">基金資產</t>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">淨資產</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 22,987,429,104</t>
+    <t xml:space="preserve">NTD 23,619,014,811</t>
   </si>
   <si>
     <t xml:space="preserve">流通在外單位數</t>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">每單位淨值</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 16.31</t>
+    <t xml:space="preserve">NTD 16.76</t>
   </si>
   <si>
     <t xml:space="preserve">項目</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">股票</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 22,291,055,940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.97%</t>
+    <t xml:space="preserve">NTD 23,246,184,096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.42%</t>
   </si>
   <si>
     <t xml:space="preserve">現金</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 454,472,063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98%</t>
+    <t xml:space="preserve">NTD 707,891,387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00%</t>
   </si>
   <si>
     <t xml:space="preserve">期貨保證金</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">USD 1,000,365.79</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14%</t>
+    <t xml:space="preserve">0.13%</t>
   </si>
   <si>
     <t xml:space="preserve">申贖應付款</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">NTD -8,227,500</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.04%</t>
+    <t xml:space="preserve">-0.03%</t>
   </si>
   <si>
     <t xml:space="preserve">應收付證券款</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 146,344,050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64%</t>
+    <t xml:space="preserve">NTD -347,993,843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.47%</t>
   </si>
   <si>
     <t xml:space="preserve">股票代號</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">53,000</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16%</t>
+    <t xml:space="preserve">6.23%</t>
   </si>
   <si>
     <t xml:space="preserve">SNDK US</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">34,400</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40%</t>
+    <t xml:space="preserve">4.54%</t>
   </si>
   <si>
     <t xml:space="preserve">BE US</t>
@@ -143,10 +143,34 @@
     <t xml:space="preserve">BLOOM ENERGY CORP- A</t>
   </si>
   <si>
-    <t xml:space="preserve">115,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75%</t>
+    <t xml:space="preserve">125,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIEN US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIENA CORP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台光電</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24%</t>
   </si>
   <si>
     <t xml:space="preserve">MRVL US</t>
@@ -158,21 +182,6 @@
     <t xml:space="preserve">148,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIEN US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIENA CORP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33%</t>
-  </si>
-  <si>
     <t xml:space="preserve">6787 JP</t>
   </si>
   <si>
@@ -182,6 +191,18 @@
     <t xml:space="preserve">130,000</t>
   </si>
   <si>
+    <t xml:space="preserve">3.20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMD US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADVANCED MICRO DEVICES.amd us(超微半導體公司)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68,000</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.15%</t>
   </si>
   <si>
@@ -194,16 +215,16 @@
     <t xml:space="preserve">3.11%</t>
   </si>
   <si>
-    <t xml:space="preserve">2383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">台光電</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05%</t>
+    <t xml:space="preserve">2454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">聯發科</t>
+  </si>
+  <si>
+    <t xml:space="preserve">285,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94%</t>
   </si>
   <si>
     <t xml:space="preserve">009150 KS</t>
@@ -215,19 +236,7 @@
     <t xml:space="preserve">41,177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMD US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADVANCED MICRO DEVICES.amd us(超微半導體公司)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85%</t>
+    <t xml:space="preserve">2.92%</t>
   </si>
   <si>
     <t xml:space="preserve">GLW US</t>
@@ -239,7 +248,31 @@
     <t xml:space="preserve">120,700</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81%</t>
+    <t xml:space="preserve">2.83%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇鋐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5801 JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FURUKAWA ELECTRIC CO LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58%</t>
   </si>
   <si>
     <t xml:space="preserve">6515</t>
@@ -251,7 +284,7 @@
     <t xml:space="preserve">60,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80%</t>
+    <t xml:space="preserve">2.56%</t>
   </si>
   <si>
     <t xml:space="preserve">COHR US</t>
@@ -263,19 +296,7 @@
     <t xml:space="preserve">57,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5801 JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FURUKAWA ELECTRIC CO LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63%</t>
+    <t xml:space="preserve">2.55%</t>
   </si>
   <si>
     <t xml:space="preserve">GEV US</t>
@@ -287,33 +308,9 @@
     <t xml:space="preserve">16,400</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇鋐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215,000</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.51%</t>
   </si>
   <si>
-    <t xml:space="preserve">2454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">聯發科</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41%</t>
-  </si>
-  <si>
     <t xml:space="preserve">3037</t>
   </si>
   <si>
@@ -323,9 +320,6 @@
     <t xml:space="preserve">750,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38%</t>
-  </si>
-  <si>
     <t xml:space="preserve">2308</t>
   </si>
   <si>
@@ -335,7 +329,7 @@
     <t xml:space="preserve">257,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21%</t>
+    <t xml:space="preserve">2.26%</t>
   </si>
   <si>
     <t xml:space="preserve">ENR GY</t>
@@ -347,7 +341,7 @@
     <t xml:space="preserve">75,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20%</t>
+    <t xml:space="preserve">2.19%</t>
   </si>
   <si>
     <t xml:space="preserve">FORM US</t>
@@ -359,7 +353,7 @@
     <t xml:space="preserve">105,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14%</t>
+    <t xml:space="preserve">2.17%</t>
   </si>
   <si>
     <t xml:space="preserve">5274</t>
@@ -371,7 +365,7 @@
     <t xml:space="preserve">30,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05%</t>
+    <t xml:space="preserve">2.08%</t>
   </si>
   <si>
     <t xml:space="preserve">GOOGL US</t>
@@ -383,34 +377,37 @@
     <t xml:space="preserve">44,000</t>
   </si>
   <si>
+    <t xml:space="preserve">2.02%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TER US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERADYNE INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5706 JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsui Mining ＆ Smelting Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94%</t>
+  </si>
+  <si>
     <t xml:space="preserve">WDC US</t>
   </si>
   <si>
     <t xml:space="preserve">WESTERN DIGITAL CORP</t>
   </si>
   <si>
-    <t xml:space="preserve">35,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TER US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERADYNE INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5706 JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitsui Mining ＆ Smelting Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90%</t>
+    <t xml:space="preserve">1.89%</t>
   </si>
   <si>
     <t xml:space="preserve">7826 JP</t>
@@ -422,7 +419,7 @@
     <t xml:space="preserve">280,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75%</t>
+    <t xml:space="preserve">1.74%</t>
   </si>
   <si>
     <t xml:space="preserve">2330</t>
@@ -434,7 +431,19 @@
     <t xml:space="preserve">177,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60%</t>
+    <t xml:space="preserve">1.64%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3110 JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NITTO BOSEKI CO LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63,200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45%</t>
   </si>
   <si>
     <t xml:space="preserve">285A JP</t>
@@ -446,7 +455,7 @@
     <t xml:space="preserve">50,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52%</t>
+    <t xml:space="preserve">1.44%</t>
   </si>
   <si>
     <t xml:space="preserve">HOT GY</t>
@@ -458,7 +467,19 @@
     <t xml:space="preserve">20,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50%</t>
+    <t xml:space="preserve">1.43%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVGO US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROADCOM LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41%</t>
   </si>
   <si>
     <t xml:space="preserve">AIXA GY</t>
@@ -470,28 +491,7 @@
     <t xml:space="preserve">192,539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVGO US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROADCOM LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3110 JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NITTO BOSEKI CO LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63,200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39%</t>
+    <t xml:space="preserve">1.40%</t>
   </si>
   <si>
     <t xml:space="preserve">3711</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">600,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21%</t>
+    <t xml:space="preserve">1.26%</t>
   </si>
   <si>
     <t xml:space="preserve">SOI FP</t>
@@ -515,7 +515,19 @@
     <t xml:space="preserve">68,198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17%</t>
+    <t xml:space="preserve">1.20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5803 JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUJIKURA LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06%</t>
   </si>
   <si>
     <t xml:space="preserve">6997 JP</t>
@@ -527,16 +539,7 @@
     <t xml:space="preserve">550,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5803 JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUJIKURA LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210,000</t>
+    <t xml:space="preserve">1.05%</t>
   </si>
   <si>
     <t xml:space="preserve">2360</t>
@@ -548,7 +551,7 @@
     <t xml:space="preserve">120,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01%</t>
+    <t xml:space="preserve">0.98%</t>
   </si>
   <si>
     <t xml:space="preserve">VIAV US</t>
@@ -560,7 +563,7 @@
     <t xml:space="preserve">150,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95%</t>
+    <t xml:space="preserve">0.96%</t>
   </si>
   <si>
     <t xml:space="preserve">6869 HK</t>
@@ -572,7 +575,7 @@
     <t xml:space="preserve">220,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90%</t>
+    <t xml:space="preserve">0.83%</t>
   </si>
   <si>
     <t xml:space="preserve">NVDA US</t>
@@ -581,18 +584,15 @@
     <t xml:space="preserve">NVIDIA CORP(輝達公司)</t>
   </si>
   <si>
+    <t xml:space="preserve">ONTO US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONTO INNOVATION INC</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.82%</t>
   </si>
   <si>
-    <t xml:space="preserve">ONTO US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONTO INNOVATION INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80%</t>
-  </si>
-  <si>
     <t xml:space="preserve">HOOD US</t>
   </si>
   <si>
@@ -602,13 +602,25 @@
     <t xml:space="preserve">70,000</t>
   </si>
   <si>
+    <t xml:space="preserve">0.79%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4062 JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBIDEN CO LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73%</t>
+  </si>
+  <si>
     <t xml:space="preserve">AXTI US</t>
   </si>
   <si>
     <t xml:space="preserve">AXT INC</t>
   </si>
   <si>
-    <t xml:space="preserve">0.70%</t>
+    <t xml:space="preserve">0.69%</t>
   </si>
   <si>
     <t xml:space="preserve">268A JP</t>
@@ -620,7 +632,19 @@
     <t xml:space="preserve">300,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66%</t>
+    <t xml:space="preserve">0.61%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">006400 KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung SDI Co Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46%</t>
   </si>
   <si>
     <t xml:space="preserve">BKSY US</t>
@@ -629,22 +653,10 @@
     <t xml:space="preserve">BLACKSKY TECHNOLOGY INC</t>
   </si>
   <si>
-    <t xml:space="preserve">105,224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">006400 KS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung SDI Co Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47%</t>
+    <t xml:space="preserve">95,622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43%</t>
   </si>
   <si>
     <t xml:space="preserve">RKLB US</t>
@@ -656,16 +668,13 @@
     <t xml:space="preserve">40,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46%</t>
-  </si>
-  <si>
     <t xml:space="preserve">NBIS US</t>
   </si>
   <si>
     <t xml:space="preserve">NEBIUS GROUP NV</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43%</t>
+    <t xml:space="preserve">0.39%</t>
   </si>
 </sst>
 </file>
@@ -744,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
@@ -826,6 +835,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1430,10 +1451,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.75" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="24.9" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="60" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="9.6" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="10.35" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1669,18 +1690,18 @@
         <v>55</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="C27" s="57" t="s">
         <v>58</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>51</v>
       </c>
       <c r="D27" s="58" t="s">
         <v>59</v>
@@ -1708,332 +1729,332 @@
         <v>65</v>
       </c>
       <c r="C29" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="66" t="s">
         <v>66</v>
-      </c>
-      <c r="D29" s="66" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="C30" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="69" t="s">
+      <c r="D30" s="70" t="s">
         <v>70</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="72" t="s">
+      <c r="C31" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="73" t="s">
+      <c r="D31" s="74" t="s">
         <v>74</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="76" t="s">
+      <c r="C32" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="77" t="s">
+      <c r="D32" s="78" t="s">
         <v>78</v>
-      </c>
-      <c r="D32" s="78" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="80" t="s">
+      <c r="C33" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="D33" s="82" t="s">
         <v>82</v>
-      </c>
-      <c r="D33" s="82" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="84" t="s">
+      <c r="C34" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="D34" s="86" t="s">
         <v>86</v>
-      </c>
-      <c r="D34" s="86" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="88" t="s">
+      <c r="C35" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="D35" s="90" t="s">
         <v>90</v>
-      </c>
-      <c r="D35" s="90" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="92" t="s">
+      <c r="C36" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="D36" s="94" t="s">
         <v>94</v>
-      </c>
-      <c r="D36" s="94" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="C37" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="97" t="s">
+      <c r="D37" s="98" t="s">
         <v>98</v>
-      </c>
-      <c r="D37" s="98" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="100" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="100" t="s">
+      <c r="C38" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="101" t="s">
-        <v>102</v>
-      </c>
       <c r="D38" s="102" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="103" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="104" t="s">
+      <c r="D39" s="106" t="s">
         <v>105</v>
-      </c>
-      <c r="C39" s="105" t="s">
-        <v>106</v>
-      </c>
-      <c r="D39" s="106" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="107" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="108" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="109" t="s">
         <v>108</v>
       </c>
-      <c r="B40" s="108" t="s">
+      <c r="D40" s="110" t="s">
         <v>109</v>
-      </c>
-      <c r="C40" s="109" t="s">
-        <v>110</v>
-      </c>
-      <c r="D40" s="110" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="111" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="112" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="113" t="s">
         <v>112</v>
       </c>
-      <c r="B41" s="112" t="s">
+      <c r="D41" s="114" t="s">
         <v>113</v>
-      </c>
-      <c r="C41" s="113" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="114" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="115" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="116" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="117" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="116" t="s">
+      <c r="D42" s="118" t="s">
         <v>117</v>
-      </c>
-      <c r="C42" s="117" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="118" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="119" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="120" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="121" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="120" t="s">
+      <c r="D43" s="122" t="s">
         <v>121</v>
-      </c>
-      <c r="C43" s="121" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="122" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="123" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" s="124" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="124" t="s">
+      <c r="C44" s="125" t="s">
         <v>124</v>
       </c>
-      <c r="C44" s="125" t="s">
+      <c r="D44" s="126" t="s">
         <v>125</v>
-      </c>
-      <c r="D44" s="126" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="128" t="s">
+      <c r="C45" s="129" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="130" t="s">
         <v>128</v>
-      </c>
-      <c r="C45" s="129" t="s">
-        <v>125</v>
-      </c>
-      <c r="D45" s="130" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="131" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="132" t="s">
+      <c r="C46" s="133" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="134" t="s">
         <v>131</v>
-      </c>
-      <c r="C46" s="133" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" s="134" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="135" t="s">
+        <v>132</v>
+      </c>
+      <c r="B47" s="136" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="136" t="s">
+      <c r="C47" s="137" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="137" t="s">
+      <c r="D47" s="138" t="s">
         <v>135</v>
-      </c>
-      <c r="D47" s="138" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="139" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="140" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="140" t="s">
+      <c r="C48" s="141" t="s">
         <v>138</v>
       </c>
-      <c r="C48" s="141" t="s">
+      <c r="D48" s="142" t="s">
         <v>139</v>
-      </c>
-      <c r="D48" s="142" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="143" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="144" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="144" t="s">
+      <c r="C49" s="145" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="145" t="s">
+      <c r="D49" s="146" t="s">
         <v>143</v>
-      </c>
-      <c r="D49" s="146" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="147" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" s="148" t="s">
         <v>145</v>
       </c>
-      <c r="B50" s="148" t="s">
+      <c r="C50" s="149" t="s">
         <v>146</v>
       </c>
-      <c r="C50" s="149" t="s">
+      <c r="D50" s="150" t="s">
         <v>147</v>
-      </c>
-      <c r="D50" s="150" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="151" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="152" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="152" t="s">
+      <c r="C51" s="153" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="153" t="s">
+      <c r="D51" s="154" t="s">
         <v>151</v>
-      </c>
-      <c r="D51" s="154" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="155" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="156" t="s">
         <v>153</v>
       </c>
-      <c r="B52" s="156" t="s">
+      <c r="C52" s="157" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="157" t="s">
+      <c r="D52" s="158" t="s">
         <v>155</v>
-      </c>
-      <c r="D52" s="158" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="53">
@@ -2103,63 +2124,63 @@
         <v>174</v>
       </c>
       <c r="D57" s="178" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="179" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B58" s="180" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C58" s="181" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D58" s="182" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="183" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B59" s="184" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C59" s="185" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D59" s="186" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="187" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B60" s="188" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C60" s="189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D60" s="190" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="191" t="s">
+        <v>188</v>
+      </c>
+      <c r="B61" s="192" t="s">
+        <v>189</v>
+      </c>
+      <c r="C61" s="193" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="194" t="s">
         <v>187</v>
-      </c>
-      <c r="B61" s="192" t="s">
-        <v>188</v>
-      </c>
-      <c r="C61" s="193" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" s="194" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="62">
@@ -2170,7 +2191,7 @@
         <v>191</v>
       </c>
       <c r="C62" s="197" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D62" s="198" t="s">
         <v>192</v>
@@ -2187,32 +2208,32 @@
         <v>195</v>
       </c>
       <c r="D63" s="202" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="203" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B64" s="204" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C64" s="205" t="s">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="D64" s="206" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="207" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B65" s="208" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C65" s="209" t="s">
-        <v>201</v>
+        <v>62</v>
       </c>
       <c r="D65" s="210" t="s">
         <v>202</v>
@@ -2268,10 +2289,24 @@
         <v>216</v>
       </c>
       <c r="C69" s="225" t="s">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="D69" s="226" t="s">
-        <v>217</v>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="227" t="s">
+        <v>218</v>
+      </c>
+      <c r="B70" s="228" t="s">
+        <v>219</v>
+      </c>
+      <c r="C70" s="229" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70" s="230" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
